--- a/VRP_results_kg_10farmers_basecase.xlsx
+++ b/VRP_results_kg_10farmers_basecase.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="9">
@@ -3631,7 +3631,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="29">
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3903,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="45">
@@ -3920,7 +3920,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="46">
@@ -3937,7 +3937,7 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="47">
@@ -3954,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="48">
@@ -3971,7 +3971,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="49">
@@ -4005,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="51">
@@ -4022,7 +4022,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="52">
@@ -4464,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4566,7 +4566,7 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="84">
@@ -4600,7 +4600,7 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="86">
@@ -4634,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4651,7 +4651,7 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5127,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5178,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="120">
@@ -5195,7 +5195,7 @@
         <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="121">
@@ -5263,7 +5263,7 @@
         <v>3</v>
       </c>
       <c r="E124" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5790,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="156">
@@ -5807,7 +5807,7 @@
         <v>2</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="157">
@@ -6657,7 +6657,7 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -6708,7 +6708,7 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="210">
@@ -7337,7 +7337,7 @@
         <v>2</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="247">
@@ -7354,7 +7354,7 @@
         <v>3</v>
       </c>
       <c r="E247" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -7439,7 +7439,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="253">
@@ -7558,7 +7558,7 @@
         <v>3</v>
       </c>
       <c r="E259" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -7881,7 +7881,7 @@
         <v>1</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="279">
@@ -7932,7 +7932,7 @@
         <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="282">
@@ -7949,7 +7949,7 @@
         <v>2</v>
       </c>
       <c r="E282" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="283">
@@ -7966,7 +7966,7 @@
         <v>3</v>
       </c>
       <c r="E283" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="284">
@@ -8187,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="297">
@@ -8544,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -8561,7 +8561,7 @@
         <v>2</v>
       </c>
       <c r="E318" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -8578,7 +8578,7 @@
         <v>3</v>
       </c>
       <c r="E319" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -8748,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="E329" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -8782,7 +8782,7 @@
         <v>3</v>
       </c>
       <c r="E331" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -8799,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="E332" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="333">
@@ -8816,7 +8816,7 @@
         <v>2</v>
       </c>
       <c r="E333" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="334">
@@ -8833,7 +8833,7 @@
         <v>3</v>
       </c>
       <c r="E334" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="335">
@@ -8850,7 +8850,7 @@
         <v>1</v>
       </c>
       <c r="E335" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="336">
@@ -8901,7 +8901,7 @@
         <v>1</v>
       </c>
       <c r="E338" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -16888,7 +16888,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -16972,7 +16972,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -17126,7 +17126,7 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -18078,7 +18078,7 @@
         <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="96">
@@ -18246,7 +18246,7 @@
         <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -18302,7 +18302,7 @@
         <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -18316,7 +18316,7 @@
         <v>3</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="113">
@@ -18344,7 +18344,7 @@
         <v>5</v>
       </c>
       <c r="D114" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -20833,7 +20833,7 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="90">
@@ -20850,7 +20850,7 @@
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="91">
@@ -20867,7 +20867,7 @@
         <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="92">
@@ -21156,7 +21156,7 @@
         <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="109">
@@ -28534,7 +28534,7 @@
         <v>1</v>
       </c>
       <c r="E542" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="543">
@@ -28551,7 +28551,7 @@
         <v>2</v>
       </c>
       <c r="E543" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="544">
@@ -28568,7 +28568,7 @@
         <v>3</v>
       </c>
       <c r="E544" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="545">
@@ -28602,7 +28602,7 @@
         <v>2</v>
       </c>
       <c r="E546" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="547">
@@ -28738,7 +28738,7 @@
         <v>1</v>
       </c>
       <c r="E554" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="555">
@@ -28755,7 +28755,7 @@
         <v>2</v>
       </c>
       <c r="E555" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="556">
@@ -28772,7 +28772,7 @@
         <v>3</v>
       </c>
       <c r="E556" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="557">
@@ -28789,7 +28789,7 @@
         <v>1</v>
       </c>
       <c r="E557" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="558">
@@ -28806,7 +28806,7 @@
         <v>2</v>
       </c>
       <c r="E558" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="559">
@@ -28823,7 +28823,7 @@
         <v>3</v>
       </c>
       <c r="E559" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="560">
@@ -42345,7 +42345,7 @@
         <v>1</v>
       </c>
       <c r="E542" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="543">
@@ -42362,7 +42362,7 @@
         <v>2</v>
       </c>
       <c r="E543" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="544">
@@ -42379,7 +42379,7 @@
         <v>3</v>
       </c>
       <c r="E544" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="545">
@@ -42549,7 +42549,7 @@
         <v>1</v>
       </c>
       <c r="E554" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="555">
@@ -42566,7 +42566,7 @@
         <v>2</v>
       </c>
       <c r="E555" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="556">
@@ -42583,7 +42583,7 @@
         <v>3</v>
       </c>
       <c r="E556" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="557">
@@ -48404,7 +48404,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="87">
@@ -48421,7 +48421,7 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="88">
@@ -48438,7 +48438,7 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="89">
@@ -48727,7 +48727,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="106">
@@ -51532,7 +51532,7 @@
         <v>2</v>
       </c>
       <c r="E270" t="n">
-        <v>27.3607</v>
+        <v>27.3608</v>
       </c>
     </row>
     <row r="271">
@@ -56105,7 +56105,7 @@
         <v>1</v>
       </c>
       <c r="E539" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="540">
@@ -56122,7 +56122,7 @@
         <v>2</v>
       </c>
       <c r="E540" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="541">
@@ -56139,7 +56139,7 @@
         <v>3</v>
       </c>
       <c r="E541" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="542">
@@ -56173,7 +56173,7 @@
         <v>2</v>
       </c>
       <c r="E543" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="544">
@@ -56309,7 +56309,7 @@
         <v>1</v>
       </c>
       <c r="E551" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="552">
@@ -56326,7 +56326,7 @@
         <v>2</v>
       </c>
       <c r="E552" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="553">
@@ -56343,7 +56343,7 @@
         <v>3</v>
       </c>
       <c r="E553" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="554">
@@ -56360,7 +56360,7 @@
         <v>1</v>
       </c>
       <c r="E554" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="555">
@@ -56377,7 +56377,7 @@
         <v>2</v>
       </c>
       <c r="E555" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="556">
@@ -56394,7 +56394,7 @@
         <v>3</v>
       </c>
       <c r="E556" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="557">
